--- a/protocols/Giovanni_s_Protocols/cellular/CB5.Cell line media.xlsx
+++ b/protocols/Giovanni_s_Protocols/cellular/CB5.Cell line media.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/GoogleDrive/My Drive/protocols/CELL LINES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/goldrath/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEB3F5C-9322-2941-A1C9-7C90CE0CF1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31A4BCBB-7773-E14F-9EDA-7F3E39856ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="760" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="220204_celllines&amp;media_GG_001" sheetId="1" r:id="rId1"/>
@@ -106,6 +106,7 @@
         <sz val="10"/>
         <color theme="5"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>note:</t>
     </r>
@@ -115,6 +116,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> this is a selection marker to maintain gp33-41 expression</t>
     </r>
@@ -190,9 +192,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -204,6 +203,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -211,6 +211,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -218,12 +219,14 @@
       <sz val="10"/>
       <color theme="5"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -286,18 +289,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,618 +515,483 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z70"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-    </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="3" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="3" t="s">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="3" t="s">
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="2"/>
-      <c r="Z26" s="2"/>
-    </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="3" t="s">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="3" t="s">
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L28" s="7"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="7"/>
-    </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="3" t="s">
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="3" t="s">
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="5" t="s">
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L31" s="3"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="6" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="6" t="s">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="2"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="2"/>
-      <c r="W38" s="2"/>
-      <c r="X38" s="2"/>
-      <c r="Y38" s="2"/>
-      <c r="Z38" s="2"/>
-    </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="3" t="s">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="3" t="s">
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="3" t="s">
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="3" t="s">
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="6" t="s">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="6" t="s">
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="6" t="s">
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="6" t="s">
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="6" t="s">
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="6" t="s">
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="10"/>
-    </row>
-    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C49" s="5"/>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="2"/>
-      <c r="T50" s="2"/>
-      <c r="U50" s="2"/>
-      <c r="V50" s="2"/>
-      <c r="W50" s="2"/>
-      <c r="X50" s="2"/>
-      <c r="Y50" s="2"/>
-      <c r="Z50" s="2"/>
-    </row>
-    <row r="51" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A51" s="5" t="s">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A51" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A52" s="6" t="s">
+    <row r="52" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A52" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A53" s="6" t="s">
+    <row r="53" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A53" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A54" s="6" t="s">
+    <row r="54" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A54" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A55" s="6" t="s">
+    <row r="55" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A55" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A56" s="9" t="s">
+    <row r="56" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A56" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A57" s="10" t="s">
+    <row r="57" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A57" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A58" s="10" t="s">
+    <row r="58" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A58" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:26" ht="13" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
-      <c r="T59" s="2"/>
-      <c r="U59" s="2"/>
-      <c r="V59" s="2"/>
-      <c r="W59" s="2"/>
-      <c r="X59" s="2"/>
-      <c r="Y59" s="2"/>
-      <c r="Z59" s="2"/>
-    </row>
-    <row r="60" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A60" s="5" t="s">
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A60" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A61" s="6" t="s">
+    <row r="61" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A61" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A62" s="6" t="s">
+    <row r="62" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A62" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A63" s="6" t="s">
+    <row r="63" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A63" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:26" ht="13" x14ac:dyDescent="0.15">
-      <c r="A64" s="6" t="s">
+    <row r="64" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A64" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>47</v>
       </c>
     </row>
